--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -1,43 +1,421 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\remotion\src\episodes\episode-03\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView windowWidth="23040" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>镜头描述</t>
+  </si>
+  <si>
+    <t>时长（单位：秒）</t>
+  </si>
+  <si>
+    <t>画面描述</t>
+  </si>
+  <si>
+    <t>提示词</t>
+  </si>
+  <si>
+    <t>听到群消息一响，突然心慌，身体发抖</t>
+  </si>
+  <si>
+    <t>一个在车站等车的穿着职场职业装的女孩，脸上平静。此时她的外套口袋里传来震动，是手机响了。她拿出手机，此时给出一个手持手机的特写画面，手机屏幕上是很多条工作相关的群消息。此时切到全景，她的身子不受控制地颤抖。</t>
+  </si>
+  <si>
+    <t>以参考图为首帧和视觉依据，生成一段 4 秒、9:16 竖屏的极简二维卡通动画。保持参考图中女孩的脸型、黑色齐肩发、大头小身比例、灰绿色职业装、黑色手提包，以及公交站牌和城市背景。细深灰轮廓线，低饱和配色，平涂色块，白色留白，整体安静克制。 严格按顺序表现三个阶段，仅两次切镜： 0–1.2 秒：全身景。女孩独自在公交站牌旁等车，脸上平静。外套口袋轻微抖动，表示手机震动。她立即用右手从口袋取出手机，左手始终提着黑色手提包。 1.2–2.2 秒：切到右手持手机的特写。屏幕上密集排列着工作群通知卡片，用群聊头像、短横线文字和红色未读标记表现消息很多，不要求具体文字可读。手机外形稳定，手指自然握住手机。 2.2–4 秒：切回与开头相同的全身景。女孩右手仍持手机，左手仍提包。看到通知后，她的肩膀和双手出现细小、快速、无法控制的颤抖，手机和提包随之轻微抖动；双脚始终站稳，面部仍然平静。镜头固定，背景静止，最后停留在她颤抖的画面上。 无对白、无字幕。始终只有一名女孩，角色、服装、道具和画风全程一致。颤抖局限于人物，不能表现成整个画面震动。</t>
+  </si>
+  <si>
+    <t>星期天在家休息，想到星期一要上班就莫名心慌</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -45,33 +423,543 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -85,40 +973,40 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -146,14 +1034,14 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -181,66 +1069,40 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -254,20 +1116,38 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -320,20 +1200,62 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="45.8888888888889" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="71" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.4444444444444" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88888888888889" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="288" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>镜头描述</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>星期天在家休息，想到星期一要上班就莫名心慌</t>
+  </si>
+  <si>
+    <t>一个穿可爱便服的女孩，星期天在家里，当她走过家里的日历的时候，看到第二天是星期一。忽然感到莫名的心慌，此时她捂住了自己的胸口，止不住地发抖</t>
+  </si>
+  <si>
+    <t>以参考图为首帧和视觉依据，生成一段4秒、9:16竖屏的极简二维卡通动画。保持参考图的画风：大头小身、点状五官、细而均匀的深灰轮廓线、低饱和米色和灰蓝色平涂、大量留白、安静克制的日常漫画感。室内居家场景。一个穿浅色可爱便服的年轻女孩独自在家，黑色齐肩直发，人物比例和脸型始终保持一致。背景是简化的客厅或玄关，墙上挂着一张清晰的月历，画面中能看到“星期一”或周一标记。0–1.2秒：中景。女孩从画面左侧缓慢走过墙上的月历，目光扫到第二天的星期一。她突然停住，身体短暂僵住，脸上仍保持克制的平静表情。1.2–2.4秒：女孩的右手迅速但自然地捂住胸口，肩膀微微收紧，身体向前缩起，表现突然出现的心慌。2.4–4秒：保持中景或轻微推近。女孩捂着胸口，双肩、手臂和身体开始细小而持续地发抖，颤抖逐渐明显；双脚保持站稳，不跌倒，不奔跑。月历和房间背景保持静止，突出“看到星期一后，身体先产生警报”的感觉。镜头稳定，动作连续，只有一名女孩。无对白、无旁白、无字幕。人物的发型、服装、脸型、颜色和比例全程一致。不要出现夸张哭泣或戏剧化表情。</t>
   </si>
 </sst>
 </file>
@@ -1244,15 +1250,19 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="288" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2">
         <v>4</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>镜头描述</t>
   </si>
@@ -62,6 +62,20 @@
   </si>
   <si>
     <t>以参考图为首帧和视觉依据，生成一段4秒、9:16竖屏的极简二维卡通动画。保持参考图的画风：大头小身、点状五官、细而均匀的深灰轮廓线、低饱和米色和灰蓝色平涂、大量留白、安静克制的日常漫画感。室内居家场景。一个穿浅色可爱便服的年轻女孩独自在家，黑色齐肩直发，人物比例和脸型始终保持一致。背景是简化的客厅或玄关，墙上挂着一张清晰的月历，画面中能看到“星期一”或周一标记。0–1.2秒：中景。女孩从画面左侧缓慢走过墙上的月历，目光扫到第二天的星期一。她突然停住，身体短暂僵住，脸上仍保持克制的平静表情。1.2–2.4秒：女孩的右手迅速但自然地捂住胸口，肩膀微微收紧，身体向前缩起，表现突然出现的心慌。2.4–4秒：保持中景或轻微推近。女孩捂着胸口，双肩、手臂和身体开始细小而持续地发抖，颤抖逐渐明显；双脚保持站稳，不跌倒，不奔跑。月历和房间背景保持静止，突出“看到星期一后，身体先产生警报”的感觉。镜头稳定，动作连续，只有一名女孩。无对白、无旁白、无字幕。人物的发型、服装、脸型、颜色和比例全程一致。不要出现夸张哭泣或戏剧化表情。</t>
+  </si>
+  <si>
+    <t>夜里睡不着觉，时长半夜在固定时间醒来，做梦也梦到自己在工作。</t>
+  </si>
+  <si>
+    <t>一个穿着可爱睡衣的女孩，在夜里，在床上翻身又翻回来，睡不着觉，又再次翻回去</t>
+  </si>
+  <si>
+    <t>以参考图为首帧和视觉依据，生成一段2秒、9:16竖屏的极简二维卡通动画。保持参考图的视觉风格：大头小身、点状五官、细而均匀的深灰轮廓线、低饱和深蓝和米黄色平涂、简洁留白、安静克制的漫画感。
+夜晚的卧室，中景固定机位。一个穿素色睡衣的女孩躺在床上，黑色齐肩直发，盖着浅色被子。卧室整体为深蓝灰色，头顶只有一小片柔和的淡黄色灯光。人物脸型、发型、睡衣颜色、床和枕头全程保持一致。
+0–0.7秒：女孩睁着眼睛平躺，短暂保持不动，表现难以入睡。
+0.7–1.4秒：她缓慢翻身侧躺，面朝画面外侧；被子随身体自然移动，动作幅度小而真实。
+1.4–2秒：她睁开眼，随后翻回另一侧，仍然无法入睡，她又慢慢地翻回来，变回平躺地姿势。结尾停在她睁眼平躺、安静失眠的状态。
+镜头始终固定，不推拉、不摇晃。动作连贯、速度缓慢，只有一名女孩。无对白、无旁白、无字幕。</t>
   </si>
 </sst>
 </file>
@@ -1212,8 +1226,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="45.8888888888889" style="1" customWidth="1"/>
     <col min="2" max="2" width="29.3333333333333" style="1" customWidth="1"/>
@@ -1260,8 +1274,22 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="4" ht="316.8" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>镜头描述</t>
   </si>
@@ -76,6 +76,24 @@
 0.7–1.4秒：她缓慢翻身侧躺，面朝画面外侧；被子随身体自然移动，动作幅度小而真实。
 1.4–2秒：她睁开眼，随后翻回另一侧，仍然无法入睡，她又慢慢地翻回来，变回平躺地姿势。结尾停在她睁眼平躺、安静失眠的状态。
 镜头始终固定，不推拉、不摇晃。动作连贯、速度缓慢，只有一名女孩。无对白、无旁白、无字幕。</t>
+  </si>
+  <si>
+    <t>夜里在睡眠的时候，在梦中梦到自己坐在公司的工位前，对着笔记本电脑在疯狂加班。</t>
+  </si>
+  <si>
+    <t>一个穿着素色睡衣的女孩，躺在床上，正在闭眼睡觉。此时她梦到了她在公司的工位上坐着，她穿着职场的职业装，面对着电脑正在办公，她的工位上已经堆起了一摞文件，就在她正在办公的时候，一个身着职业装的男性角色走过来，把一摞文件又摞在她原来的文件上，此时，她从梦中惊醒。</t>
+  </si>
+  <si>
+    <t>以参考图为首帧和视觉依据，生成一段4秒、9:16竖屏的极简二维卡通动画。保持参考图的画风：大头小身、点状五官、细而均匀的深灰轮廓线、低饱和灰蓝、灰绿、米色平涂、大量留白、安静克制的漫画叙事感。严格表现一个连续梦境，仅使用清晰的梦境转场：0–0.7秒：夜晚卧室中景。女孩穿素色睡衣，躺在床上闭眼睡觉，盖着浅色被子。卧室安静，深蓝灰色调，头顶有柔和淡黄色光影。人物脸型、发型和睡衣保持稳定。0.7–1.2秒：画面用柔和的淡入或轻微叠化进入梦境，不要突然闪烁。场景变成白天的简化办公室。女孩坐在自己的工位前，穿灰绿色职业装，面对电脑办公。她的黑色齐肩直发、脸型和人物比例保持一致。1.2–2.4秒：中景固定镜头。女孩继续低头办公，桌面上已经堆着一摞高高的文件，文件整齐叠放但明显带来压力感。一个穿素色职业装的男性同事从画面右侧走来，手里只拿着一摞文件。2.4–3.1秒：男性同事把手中的文件放到女孩原有的文件堆上，文件堆明显变高。男性只完成放下文件这一个动作，女孩仍坐在电脑前，动作短暂停住。3.1–4秒：女孩突然从梦中惊醒，画面快速叠化回夜晚卧室。她睁大眼睛坐起或半坐起，双手抓住被子，表情惊慌、呼吸急促但不夸张。结尾停留在她惊醒后的脸部和上半身。无对白、无旁白、无字幕。全程只有一名女性主角和一名男性同事。男性不露脸或只显示简化侧脸即可。办公室、卧室、电脑、床、文件和服装在各自场景中保持一致。镜头稳定，动作清楚，梦境转场柔和。</t>
+  </si>
+  <si>
+    <t>在会议室开会，自己在台下坐着，忽然出现走神</t>
+  </si>
+  <si>
+    <t>一个穿着职场职业装的女孩，在明亮的会议室坐着，此时同事正在讲ppt，而自己忽然出现了走神，莫名地感到腹痛，手脚发凉</t>
+  </si>
+  <si>
+    <t>以参考图为首帧和视觉依据，生成一段4秒、9:16竖屏的极简二维卡通动画。保持参考图的画风：大头小身、点状五官、细而均匀的深灰轮廓线、低饱和灰蓝、灰绿、米色平涂、大量白色留白，整体安静、克制、略带疏离感。明亮的简化会议室内，一名穿灰绿色职业装的女孩坐在会议桌旁。她有黑色齐肩直发、固定脸型和人物比例。前方是一块正在播放演示文稿的屏幕，屏幕只显示抽象的图表色块和横线，不出现可读文字。会议桌旁有两三名模糊的同事，只作为背景轮廓。0–1.2秒：中景固定镜头。同事在前方讲解PPT，女孩端坐在会议桌旁，起初看向屏幕。会议室明亮、安静，背景人物动作很少。1.2–2.2秒：女孩的视线慢慢偏离屏幕，眼神失焦，头部轻微垂下，表现短暂走神。她的右手缓慢移向腹部，身体略微收紧。2.2–3.2秒：女孩捂住腹部，眉眼收紧，嘴角轻微僵硬，表现突然出现的腹痛。她的双手和脚保持基本静止，不做夸张动作；在手指和脚踝附近加入很淡的浅蓝色冷感线条，表示手脚发凉。3.2–4秒：镜头轻微推近女孩。她仍坐在原位，手按着腹部，脸色比周围略显苍白，眼神紧张而恍惚；会议室背景继续正常进行，形成“外表还在会议中、身体已经发出警报”的反差。结尾停留在她捂腹、失神和发冷的状态。无对白、无旁白、无字幕。始终只有一名女性主角，角色、发型、服装、会议室和画风全程一致。镜头稳定，动作缓慢清楚，生理反应通过眼神、姿势、色彩和少量符号表现，不要使用夸张表演。</t>
   </si>
 </sst>
 </file>
@@ -691,12 +709,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1226,8 +1241,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="45.8888888888889" style="1" customWidth="1"/>
     <col min="2" max="2" width="29.3333333333333" style="1" customWidth="1"/>
@@ -1237,59 +1252,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="288" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="288" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" ht="316.8" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="388.8" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="409" customHeight="1" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>镜头</t>
   </si>
@@ -42,10 +42,16 @@
     <t>时长</t>
   </si>
   <si>
-    <t>文本</t>
+    <t>文本或者台词</t>
   </si>
   <si>
     <t>镜头脚本</t>
+  </si>
+  <si>
+    <t>开头真人出镜的镜头</t>
+  </si>
+  <si>
+    <t>你知道吗？你平时吃饭的习惯，暴露了你的潜在性格，甚至可能是心理创伤。</t>
   </si>
 </sst>
 </file>
@@ -661,9 +667,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -976,21 +985,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="40" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5454545454545" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43" style="1" customWidth="1"/>
+    <col min="4" max="4" width="82.0909090909091" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\remotion\src\episodes\episode-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cx\WPS Cloud Files\.566657936\cachedata\10F40C0D1042408792A11F56B9EA379A\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>镜头</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>你知道吗？你平时吃饭的习惯，暴露了你的潜在性格，甚至可能是心理创伤。</t>
+  </si>
+  <si>
+    <t>习惯把最喜欢的食物留到最后吃的人，有延迟满足的习惯，生活中更为自律</t>
   </si>
 </sst>
 </file>
@@ -985,8 +988,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.5454545454545" style="1" customWidth="1"/>
@@ -1015,6 +1018,11 @@
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:4">
+      <c r="C3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cx\WPS Cloud Files\.566657936\cachedata\10F40C0D1042408792A11F56B9EA379A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\remotion\src\episodes\episode-03\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>镜头</t>
   </si>
@@ -54,7 +54,10 @@
     <t>你知道吗？你平时吃饭的习惯，暴露了你的潜在性格，甚至可能是心理创伤。</t>
   </si>
   <si>
-    <t>习惯把最喜欢的食物留到最后吃的人，有延迟满足的习惯，生活中更为自律</t>
+    <t>习惯把最喜欢的食物留到最后吃的人，潜意识中存在“不配得感”，更善于隐忍，更为自律</t>
+  </si>
+  <si>
+    <t>这种人从小</t>
   </si>
 </sst>
 </file>
@@ -988,8 +991,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.5454545454545" style="1" customWidth="1"/>
@@ -1025,6 +1028,11 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:4">
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>镜头</t>
   </si>
@@ -57,7 +57,10 @@
     <t>习惯把最喜欢的食物留到最后吃的人，潜意识中存在“不配得感”，更善于隐忍，更为自律</t>
   </si>
   <si>
-    <t>这种人从小</t>
+    <t>这样的人，从小生活在“有条件的爱”的家庭里。只有表现得好才能获得奖励和鼓励。</t>
+  </si>
+  <si>
+    <t>潜意识中存在深深的对安全感的失控的恐惧，因此形成了隐忍，自律的性格</t>
   </si>
 </sst>
 </file>
@@ -991,8 +994,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.5454545454545" style="1" customWidth="1"/>
@@ -1028,9 +1031,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" ht="28" spans="1:4">
       <c r="C4" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:4">
+      <c r="C5" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>镜头</t>
   </si>
@@ -51,16 +51,28 @@
     <t>开头真人出镜的镜头</t>
   </si>
   <si>
-    <t>你知道吗？你平时吃饭的习惯，暴露了你的潜在性格，甚至可能是心理创伤。</t>
-  </si>
-  <si>
-    <t>习惯把最喜欢的食物留到最后吃的人，潜意识中存在“不配得感”，更善于隐忍，更为自律</t>
+    <t>你知道吗？几乎所有不健全家庭长大的孩子，都存在进食障碍。而你平时吃饭的习惯，有可能暴露了你潜在的心理创伤。</t>
+  </si>
+  <si>
+    <t>习惯把最喜欢的食物留到最后吃的人，潜意识中存在“不配得感”。</t>
   </si>
   <si>
     <t>这样的人，从小生活在“有条件的爱”的家庭里。只有表现得好才能获得奖励和鼓励。</t>
   </si>
   <si>
-    <t>潜意识中存在深深的对安全感的失控的恐惧，因此形成了隐忍，自律的性格</t>
+    <t>潜意识中存在深深的对安全感的失控的恐惧，因此形成了隐忍，自律的性格。</t>
+  </si>
+  <si>
+    <t>吃饭吃得很快，习惯狼吞虎咽的人，对外界充满了不信任感。</t>
+  </si>
+  <si>
+    <t>这种人一般生长在匮乏的家庭里，这里的匮乏指的是精神匮乏。</t>
+  </si>
+  <si>
+    <t>当精神缺乏爱和关注时，孩子就会把注意力集中在身体的生长上。尤其是食物焦虑的人，其内心的焦虑感更重，因为糖和脂肪能带来更多的愉悦感</t>
+  </si>
+  <si>
+    <t>吃饭</t>
   </si>
 </sst>
 </file>
@@ -994,8 +1006,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.5454545454545" style="1" customWidth="1"/>
@@ -1018,7 +1030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="28" spans="1:4">
+    <row r="2" ht="42" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1039,6 +1051,26 @@
     <row r="5" ht="28" spans="1:4">
       <c r="C5" s="1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:4">
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:4">
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="56" spans="1:4">
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="C9" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,12 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>镜头</t>
   </si>
   <si>
-    <t>时长</t>
+    <t>时长(单位秒)</t>
   </si>
   <si>
     <t>文本或者台词</t>
@@ -51,7 +51,10 @@
     <t>开头真人出镜的镜头</t>
   </si>
   <si>
-    <t>你知道吗？几乎所有不健全家庭长大的孩子，都存在进食障碍。而你平时吃饭的习惯，有可能暴露了你潜在的心理创伤。</t>
+    <t>你知道吗？你平时吃饭的习惯，有可能暴露了你潜在的心理创伤。</t>
+  </si>
+  <si>
+    <t>几乎所有不健全家庭长大的孩子，都存在进食障碍。</t>
   </si>
   <si>
     <t>习惯把最喜欢的食物留到最后吃的人，潜意识中存在“不配得感”。</t>
@@ -60,7 +63,7 @@
     <t>这样的人，从小生活在“有条件的爱”的家庭里。只有表现得好才能获得奖励和鼓励。</t>
   </si>
   <si>
-    <t>潜意识中存在深深的对安全感的失控的恐惧，因此形成了隐忍，自律的性格。</t>
+    <t>潜意识中存在深深的对安全感的失控的恐惧，因此成年后形成了隐忍，自律的性格。</t>
   </si>
   <si>
     <t>吃饭吃得很快，习惯狼吞虎咽的人，对外界充满了不信任感。</t>
@@ -69,10 +72,13 @@
     <t>这种人一般生长在匮乏的家庭里，这里的匮乏指的是精神匮乏。</t>
   </si>
   <si>
-    <t>当精神缺乏爱和关注时，孩子就会把注意力集中在身体的生长上。尤其是食物焦虑的人，其内心的焦虑感更重，因为糖和脂肪能带来更多的愉悦感</t>
-  </si>
-  <si>
-    <t>吃饭</t>
+    <t>食物的饱腹感为人提供了最早的精神慰藉。当精神缺乏爱和关注时，孩子就会把注意力集中在身体的生长上。而食物焦虑的人，更容易食物上瘾，因为糖和脂肪能带来更多的愉悦感。</t>
+  </si>
+  <si>
+    <t>吃饭挑剔的人， 往往在孩童时期也是被父母挑剔的人。</t>
+  </si>
+  <si>
+    <t>他们通过挑剔食物的色香味，来满足控制欲，消除内心的不确定性。</t>
   </si>
 </sst>
 </file>
@@ -688,12 +694,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1006,11 +1015,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5454545454545" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5454545454545" style="2" customWidth="1"/>
     <col min="3" max="3" width="43" style="1" customWidth="1"/>
     <col min="4" max="4" width="82.0909090909091" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
@@ -1020,19 +1029,22 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:4">
+    <row r="2" ht="28" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -1063,14 +1075,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="56" spans="1:4">
+    <row r="8" ht="28" spans="1:4">
       <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" ht="56" spans="1:4">
       <c r="C9" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:4">
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:4">
+      <c r="C11" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -1051,21 +1051,33 @@
       </c>
     </row>
     <row r="3" ht="28" spans="1:4">
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:4">
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:4">
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
       </c>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>镜头</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>几乎所有不健全家庭长大的孩子，都存在进食障碍。</t>
+  </si>
+  <si>
+    <t>参考上传的图片的风格，从孩子视角拍一张很长的餐桌：大人的脸被景深或阴影遮住，只听见断续争吵、责备或冷场声。餐桌中央摆着一盘几乎没动过的饭，孩子坐在画面边缘，手里握着餐具，却迟迟没有开始吃。镜头缓慢推近孩子的手和餐盘，环境声逐渐模糊，只留下餐具轻微碰撞声。 构图上让餐桌边缘形成压迫感，孩子周围留出明显空白；色调偏冷，食物保持日常、真实，不要用夸张的瘦弱身体或催吐等画面表现。结尾停在孩子抬眼看向大人、又低头看餐盘的瞬间，9:16，4s</t>
   </si>
   <si>
     <t>习惯把最喜欢的食物留到最后吃的人，潜意识中存在“不配得感”。</t>
@@ -694,7 +697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -703,6 +706,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1050,12 +1056,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="28" spans="1:4">
+    <row r="3" ht="84" spans="1:4">
       <c r="B3" s="2">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:4">
@@ -1063,7 +1072,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:4">
@@ -1071,7 +1080,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
@@ -1079,32 +1088,32 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" ht="56" spans="1:4">
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" ht="28" spans="1:4">
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" ht="28" spans="1:4">
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -57,7 +57,7 @@
     <t>几乎所有不健全家庭长大的孩子，都存在进食障碍。</t>
   </si>
   <si>
-    <t>参考上传的图片的风格，从孩子视角拍一张很长的餐桌：大人的脸被景深或阴影遮住，只听见断续争吵、责备或冷场声。餐桌中央摆着一盘几乎没动过的饭，孩子坐在画面边缘，手里握着餐具，却迟迟没有开始吃。镜头缓慢推近孩子的手和餐盘，环境声逐渐模糊，只留下餐具轻微碰撞声。 构图上让餐桌边缘形成压迫感，孩子周围留出明显空白；色调偏冷，食物保持日常、真实，不要用夸张的瘦弱身体或催吐等画面表现。结尾停在孩子抬眼看向大人、又低头看餐盘的瞬间，9:16，4s</t>
+    <t>参考上传的图片的风格，从孩子视角拍一张很长的餐桌：大人的脸被景深或阴影遮住，只听见断续争吵、责备或冷场声。餐桌中央摆着一盘几乎没动过的饭，孩子坐在画面边缘，手里握着餐具，却迟迟没有开始吃。镜头缓慢推近孩子的手和餐盘，环境声逐渐模糊，只留下餐具轻微碰撞声。 构图上让餐桌边缘形成压迫感，孩子周围留出明显空白；色调偏冷，食物保持日常、真实，不要用夸张的瘦弱身体或催吐等画面表现。结尾停在孩子抬眼看向大人、又低头看餐盘的瞬间，9:16，4秒钟</t>
   </si>
   <si>
     <t>习惯把最喜欢的食物留到最后吃的人，潜意识中存在“不配得感”。</t>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -697,7 +697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -706,9 +706,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1063,7 +1060,7 @@
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>镜头</t>
   </si>
@@ -63,7 +63,13 @@
     <t>习惯把最喜欢的食物留到最后吃的人，潜意识中存在“不配得感”。</t>
   </si>
   <si>
+    <t>生成视频：参考上传的图片，生成一个4s的9:16的视频。镜头中还在坐在餐桌上，面前摆着2个餐盘，盘子里分别摆着美味的食物和不美味的食物。美味的食物在盘子里闪闪发光，不美味的食物黯淡无光。孩子把装有美味的食物的盘子拿起，放在一边，然后再次拿起筷子，先吃起了不美味的食物，9:16，4s</t>
+  </si>
+  <si>
     <t>这样的人，从小生活在“有条件的爱”的家庭里。只有表现得好才能获得奖励和鼓励。</t>
+  </si>
+  <si>
+    <t>参考上传的图片，生成一个9:16的视频。孩子坐在餐桌前，先是看了看桌上的一小块蛋糕，想伸手又收回来。孩子把一张画或作业递过去，抬头观察大人的反应。镜头保持在孩子视线高度，大人只露出手和身体。大人检查后点头，把蛋糕推给孩子，顺手摸摸他的头。孩子紧绷的肩膀才放松下来。</t>
   </si>
   <si>
     <t>潜意识中存在深深的对安全感的失控的恐惧，因此成年后形成了隐忍，自律的性格。</t>
@@ -94,13 +100,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -567,137 +579,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -706,6 +718,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1064,20 +1082,26 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="28" spans="1:4">
+    <row r="4" ht="56" spans="1:4">
       <c r="B4" s="2">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" ht="28" spans="1:4">
+    <row r="5" ht="42" spans="1:4">
       <c r="B5" s="2">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:4">
@@ -1085,32 +1109,32 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="56" spans="1:4">
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="28" spans="1:4">
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" ht="28" spans="1:4">
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>镜头</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>潜意识中存在深深的对安全感的失控的恐惧，因此成年后形成了隐忍，自律的性格。</t>
+  </si>
+  <si>
+    <t>参考上传的图片生成9:16的视频。画面中，一个小孩坐在餐桌前，她的表情活泼，眼睛闪亮，桌上是一块她喜欢的蛋糕，她小心翼翼伸出手，快碰到盘子时候停住了，抬眼望向画面外。相同构图中，孩子叠化为成年人，餐桌叠化为办公桌，她穿着干练的职业装，表情冷淡，把工作文件摆放得整整齐齐，最后停在双手克制地交叠的画面</t>
   </si>
   <si>
     <t>吃饭吃得很快，习惯狼吞虎咽的人，对外界充满了不信任感。</t>
@@ -1104,37 +1107,40 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:4">
+    <row r="6" ht="56" spans="1:4">
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:4">
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="56" spans="1:4">
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="28" spans="1:4">
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="28" spans="1:4">
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>镜头</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>吃饭吃得很快，习惯狼吞虎咽的人，对外界充满了不信任感。</t>
+  </si>
+  <si>
+    <t>中近景：一个孩子身体前倾，接连把食物送入口中，上一口还没咽下，就夹起下一口。随后镜头缓慢推近。一只手拿筷子，另一只手把餐盘往自己面前拉，手臂围住餐盘。食物的残渣和油渍可以溅出盘子，表现出她吃得狼吞虎咽的感觉</t>
   </si>
   <si>
     <t>这种人一般生长在匮乏的家庭里，这里的匮乏指的是精神匮乏。</t>
@@ -1118,29 +1121,32 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="28" spans="1:4">
+    <row r="7" ht="42" spans="1:4">
       <c r="C7" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:4">
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" ht="56" spans="1:4">
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="28" spans="1:4">
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" ht="28" spans="1:4">
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -1122,6 +1122,9 @@
       </c>
     </row>
     <row r="7" ht="42" spans="1:4">
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>镜头</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>这种人一般生长在匮乏的家庭里，这里的匮乏指的是精神匮乏。</t>
+  </si>
+  <si>
+    <t>画面中，一个孩子坐在木地上画画，她的爸爸站在她背后，背对着她，在打电话，小孩快乐地回头看了看爸爸，刚刚想喊爸爸，但是爸爸却一边打着电话一边走开了。等爸爸走出了画面，女孩脸上的快乐表情没有了，脸上是失望，</t>
   </si>
   <si>
     <t>食物的饱腹感为人提供了最早的精神慰藉。当精神缺乏爱和关注时，孩子就会把注意力集中在身体的生长上。而食物焦虑的人，更容易食物上瘾，因为糖和脂肪能带来更多的愉悦感。</t>
@@ -1132,24 +1135,30 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:4">
+    <row r="8" ht="42" spans="1:4">
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="56" spans="1:4">
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="28" spans="1:4">
       <c r="C10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="28" spans="1:4">
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>镜头</t>
   </si>
@@ -90,7 +90,10 @@
     <t>画面中，一个孩子坐在木地上画画，她的爸爸站在她背后，背对着她，在打电话，小孩快乐地回头看了看爸爸，刚刚想喊爸爸，但是爸爸却一边打着电话一边走开了。等爸爸走出了画面，女孩脸上的快乐表情没有了，脸上是失望，</t>
   </si>
   <si>
-    <t>食物的饱腹感为人提供了最早的精神慰藉。当精神缺乏爱和关注时，孩子就会把注意力集中在身体的生长上。而食物焦虑的人，更容易食物上瘾，因为糖和脂肪能带来更多的愉悦感。</t>
+    <t>食物的饱腹感为人提供了最早的精神慰藉。当精神缺乏爱和关注时，孩子就会把注意力集中在身体的生长上。</t>
+  </si>
+  <si>
+    <t>而食物焦虑的人，更容易食物上瘾，因为糖和脂肪能带来更多的愉悦感。</t>
   </si>
   <si>
     <t>吃饭挑剔的人， 往往在孩童时期也是被父母挑剔的人。</t>
@@ -1045,7 +1048,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" customWidth="1"/>
@@ -1146,7 +1149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="56" spans="1:4">
+    <row r="9" ht="42" spans="1:4">
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1159,6 +1162,11 @@
     <row r="11" ht="28" spans="1:4">
       <c r="C11" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:4">
+      <c r="C12" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -721,7 +721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -730,9 +730,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1101,7 +1098,7 @@
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1112,7 +1109,7 @@
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1134,7 +1131,7 @@
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1145,11 +1142,14 @@
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" ht="42" spans="1:4">
+      <c r="B9" s="2">
+        <v>4</v>
+      </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>镜头</t>
   </si>
@@ -93,7 +93,13 @@
     <t>食物的饱腹感为人提供了最早的精神慰藉。当精神缺乏爱和关注时，孩子就会把注意力集中在身体的生长上。</t>
   </si>
   <si>
+    <t>生成视频：根据我上传的图片，生成9:16的视频。近景画面中，小孩坐在地上抚摸着自己吃的圆滚滚的肚子，脸上哈哈哈地快乐地笑得眼睛都眯了起来，嘴角还有食物的残渣，9:16，4s</t>
+  </si>
+  <si>
     <t>而食物焦虑的人，更容易食物上瘾，因为糖和脂肪能带来更多的愉悦感。</t>
+  </si>
+  <si>
+    <t>生成视频：生成视频：根据我上传的图片，生成9:16的视频。近景画面中，小孩坐在餐桌前，菜桌上摆满了很多高脂肪高糖的食物，她左手拿着一个鸡腿，右手拿着一个鸡腿，她先啃一口左手的鸡腿又啃一口右手的鸡腿，嘴边都是食物的油和残渣。9:16，4s，10s</t>
   </si>
   <si>
     <t>吃饭挑剔的人， 往往在孩童时期也是被父母挑剔的人。</t>
@@ -721,7 +727,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -732,6 +738,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1153,20 +1162,29 @@
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D9" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="10" ht="28" spans="1:4">
+    <row r="10" ht="42" spans="1:4">
+      <c r="B10" s="2">
+        <v>4</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" ht="28" spans="1:4">
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:4">
       <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>镜头</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>吃饭挑剔的人， 往往在孩童时期也是被父母挑剔的人。</t>
+  </si>
+  <si>
+    <t>生成视频：竖屏 9:16，8 秒，温柔克制的二维手绘插画动画，心理科普短视频风格，低饱和蓝灰与暖米白配色，轻微纸张纹理，人物造型简洁统一。根据上传的图片生成视频。开场是童年时期：一个东亚孩子坐在餐桌前，正准备夹菜。父母坐在画面两侧，只露出部分身体和手，其中一只手轻轻纠正孩子握筷子的姿势，另一只手调整孩子面前的餐盘。父母没有愤怒或争吵，但动作持续、带有挑剔和控制感。孩子的动作停住，低下头，神情紧张、拘谨，开始仔细检查碗里的食物。第 4 秒进行自然的匹配叠化转场：保持完全相同的机位、餐盘位置和构图，孩子逐渐变为成年后的同一个人，儿童的手叠化为成年人的手。成年人用筷子反复翻看食物，按颜色和形状分类，最后把一块不满意的食物缓慢推到餐盘边缘，表现外界的挑剔逐渐被内化。镜头缓慢推近，动作细腻自然，情绪压抑但不戏剧化，动画连贯，人物比例稳定，餐盘和筷子不变形。画面底部预留字幕安全区。无画面文字，无对白，无字幕，无水印，无标志。，9:16，4s</t>
   </si>
   <si>
     <t>他们通过挑剔食物的色香味，来满足控制欲，消除内心的不确定性。</t>
@@ -1054,7 +1057,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="40" style="1" customWidth="1"/>
@@ -1177,15 +1180,37 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" ht="28" spans="1:4">
+    <row r="11" ht="154" spans="1:4">
+      <c r="B11" s="2">
+        <v>4</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="D11" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="12" ht="28" spans="1:4">
       <c r="C12" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -1192,6 +1192,9 @@
       </c>
     </row>
     <row r="12" ht="28" spans="1:4">
+      <c r="B12" s="2">
+        <v>4</v>
+      </c>
       <c r="C12" s="1" t="s">
         <v>24</v>
       </c>

--- a/src/episodes/episode-03/script.xlsx
+++ b/src/episodes/episode-03/script.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>镜头</t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>他们通过挑剔食物的色香味，来满足控制欲，消除内心的不确定性。</t>
+  </si>
+  <si>
+    <t>生成视频：根据我上传的图片生成视频，竖屏 9:16，4秒，温柔克制的二维手绘插画动画，心理科普短视频风格，低饱和蓝灰、暖米白和少量食物自然色，细腻纸张纹理。
+固定俯拍镜头，一双成年人的手和一只圆形餐盘位于画面中心。开场时，不同颜色和质地的食物略显杂乱地混在盘中。人物握着筷子的手有些紧绷，反复观察、翻动和检查食物，把不满意的食物缓慢夹到盘子边缘。
+随后，人物仔细地重新排列食物：绿色蔬菜、红色食物和主食被分别归类，酱汁与其他食物分开，餐盘边缘的一滴汤汁被轻轻擦去。所有动作细致、克制、稍显迟疑。
+结尾时，食物形成整齐、对称、有明确边界的排列。人物停下筷子，手指逐渐放松。周围原本略显杂乱的餐桌背景也变得整洁、安静，表现人物通过建立秩序获得短暂的确定感。镜头缓慢推近，动作自然连贯，物体形态稳定。画面底部预留字幕安全区。无文字，无对白，无字幕，无水印，无标志。，10s</t>
   </si>
 </sst>
 </file>
@@ -1191,14 +1197,16 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" ht="28" spans="1:4">
+    <row r="12" ht="196" spans="1:4">
       <c r="B12" s="2">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="D13" s="4"/>
